--- a/lang/bg/headTags.xlsx
+++ b/lang/bg/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1209</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2067">
   <si>
     <t>en</t>
   </si>
@@ -4972,6 +4972,18 @@
     <t>Shulker</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (Вдъхновено)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift (Ванилия)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -5761,6 +5773,12 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
+    <t>Умамусуме</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -6014,6 +6032,12 @@
   </si>
   <si>
     <t>Зима</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Зимна колекция</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -6540,7 +6564,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1205"/>
+  <dimension ref="A1:B1209"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14248,36 +14272,36 @@
         <v>1651</v>
       </c>
       <c r="B963" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B964" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="B965" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="B966" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B967" t="s">
         <v>1657</v>
@@ -14312,20 +14336,20 @@
         <v>1664</v>
       </c>
       <c r="B971" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B972" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B973" t="s">
         <v>1668</v>
@@ -14376,44 +14400,44 @@
         <v>1679</v>
       </c>
       <c r="B979" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B980" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="B981" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="B982" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B983" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B984" t="s">
         <v>1686</v>
@@ -14488,28 +14512,28 @@
         <v>1703</v>
       </c>
       <c r="B993" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B994" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="B995" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B996" t="s">
         <v>1708</v>
@@ -14520,52 +14544,52 @@
         <v>1709</v>
       </c>
       <c r="B997" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B998" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="B999" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="B1000" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1001" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1002" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1003" t="s">
         <v>1718</v>
@@ -14576,44 +14600,44 @@
         <v>1719</v>
       </c>
       <c r="B1004" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1005" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="B1006" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1007" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B1008" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1009" t="s">
         <v>1727</v>
@@ -14624,36 +14648,36 @@
         <v>1728</v>
       </c>
       <c r="B1010" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1011" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="B1012" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B1013" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1014" t="s">
         <v>1734</v>
@@ -14680,36 +14704,36 @@
         <v>1739</v>
       </c>
       <c r="B1017" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B1018" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B1019" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="B1020" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B1021" t="s">
         <v>1745</v>
@@ -14720,52 +14744,52 @@
         <v>1746</v>
       </c>
       <c r="B1022" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1023" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="B1024" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="B1025" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B1026" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1027" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B1028" t="s">
         <v>1755</v>
@@ -14784,28 +14808,28 @@
         <v>1758</v>
       </c>
       <c r="B1030" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1031" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="B1032" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B1033" t="s">
         <v>1763</v>
@@ -14864,76 +14888,76 @@
         <v>1776</v>
       </c>
       <c r="B1040" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1041" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="B1042" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="B1043" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="B1044" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="B1045" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="B1046" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="B1047" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="B1048" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1049" t="s">
         <v>1787</v>
@@ -14952,20 +14976,20 @@
         <v>1790</v>
       </c>
       <c r="B1051" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B1052" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1053" t="s">
         <v>1794</v>
@@ -15240,20 +15264,20 @@
         <v>1861</v>
       </c>
       <c r="B1087" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1088" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1089" t="s">
         <v>1865</v>
@@ -15272,44 +15296,44 @@
         <v>1868</v>
       </c>
       <c r="B1091" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1092" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="B1093" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B1094" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1095" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1096" t="s">
         <v>1876</v>
@@ -15320,20 +15344,20 @@
         <v>1877</v>
       </c>
       <c r="B1097" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B1098" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1099" t="s">
         <v>1881</v>
@@ -15360,20 +15384,20 @@
         <v>1886</v>
       </c>
       <c r="B1102" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B1103" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B1104" t="s">
         <v>1890</v>
@@ -15400,20 +15424,20 @@
         <v>1895</v>
       </c>
       <c r="B1107" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B1108" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B1109" t="s">
         <v>1899</v>
@@ -15448,20 +15472,20 @@
         <v>1906</v>
       </c>
       <c r="B1113" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1114" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B1115" t="s">
         <v>1910</v>
@@ -15480,60 +15504,60 @@
         <v>1913</v>
       </c>
       <c r="B1117" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1118" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="B1119" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="B1120" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="B1121" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="B1122" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="B1123" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1124" t="s">
         <v>1923</v>
@@ -15544,44 +15568,44 @@
         <v>1924</v>
       </c>
       <c r="B1125" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1126" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1127" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="B1128" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1129" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1130" t="s">
         <v>1933</v>
@@ -15720,108 +15744,108 @@
         <v>1966</v>
       </c>
       <c r="B1147" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1148" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="B1149" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B1150" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="B1151" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="B1152" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="B1153" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1154" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1155" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="B1156" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="B1157" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="B1158" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="B1159" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B1160" t="s">
         <v>1984</v>
@@ -15888,36 +15912,36 @@
         <v>1999</v>
       </c>
       <c r="B1168" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B1169" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B1170" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B1171" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B1172" t="s">
         <v>2007</v>
@@ -15936,156 +15960,156 @@
         <v>2010</v>
       </c>
       <c r="B1174" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B1175" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="B1176" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="B1177" t="s">
-        <v>2013</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="B1178" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="B1179" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B1180" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B1181" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B1182" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B1183" t="s">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B1184" t="s">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="B1185" t="s">
-        <v>2023</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="B1186" t="s">
-        <v>2024</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="B1187" t="s">
-        <v>2025</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="B1188" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B1189" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B1190" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="B1191" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B1192" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B1193" t="s">
         <v>2036</v>
@@ -16120,44 +16144,44 @@
         <v>2043</v>
       </c>
       <c r="B1197" t="s">
-        <v>801</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B1198" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="B1199" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="B1200" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="B1201" t="s">
-        <v>2050</v>
+        <v>801</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B1202" t="s">
         <v>2052</v>
@@ -16187,8 +16211,40 @@
         <v>2058</v>
       </c>
     </row>
+    <row r="1206" spans="1:2">
+      <c r="A1206" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2">
+      <c r="A1207" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2">
+      <c r="A1208" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2">
+      <c r="A1209" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>2066</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1205"/>
+  <autoFilter ref="A1:B1209"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
